--- a/docs/StructureDefinition-VAERSImmunization-vac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-vac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file ADERS (undefined) to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -237,7 +237,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+    <t>Mapping: VA Adverse Drug Event Reporting System (VA ADERS)</t>
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
@@ -675,7 +675,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1878: source value from ADERS - 17_Vac1_TypeBrand</t>
+    <t>1878: source value from ADERS - 17_Vac1_TypeBrand (A-17.11)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -701,7 +701,7 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
-    <t>1876: reference from ADERS - 0_Pt_ICN_Full</t>
+    <t>1876: reference from ADERS - 0_Pt_ICN_Full (A-0)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -786,7 +786,7 @@
 </t>
   </si>
   <si>
-    <t>1875: transform using concat(4_VacDate, 4_VacTime)</t>
+    <t>1875: transform using concat(4_VacDate, 4_VacTime) on ADERS - (A-)</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -980,7 +980,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1883: source value from ADERS - 17_Vac1_Mfgr</t>
+    <t>1883: source value from ADERS - 17_Vac1_Mfgr (A-17.13)</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -992,7 +992,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1884: source value from ADERS - 17_Vac1_Lot</t>
+    <t>1884: source value from ADERS - 17_Vac1_Lot (A-17.14)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1038,7 +1038,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1885: source value from ADERS - 17_Vac1_Site</t>
+    <t>1885: source value from ADERS - 17_Vac1_Site (A-17.15)</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1086,7 +1086,7 @@
     <t>Immunization.route.text</t>
   </si>
   <si>
-    <t>1879: source value from ADERS - 17_Vac1_Route</t>
+    <t>1879: source value from ADERS - 17_Vac1_Route (A-17.12)</t>
   </si>
   <si>
     <t>Immunization.doseQuantity</t>
@@ -1534,7 +1534,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1886: source value from ADERS - 17_Vac1_DoseInSeries</t>
+    <t>1886: source value from ADERS - 17_Vac1_DoseInSeries (A-17.16)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1898,7 +1898,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="67.44921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="147.5546875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VAERSImmunization-vac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-vac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunization-vac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-vac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunization-vac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-vac1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="495">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to Immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-immunization</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Immunization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -274,11 +274,11 @@
     <t>Immunization event information</t>
   </si>
   <si>
-    <t>\-</t>
+    <t>Describes the event of a patient being administered a vaccine or a record of an immunization as reported by a patient, a clinician or another party.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}us-core-5:SHOULD have a translation to the NDC value set {vaccineCode.coding.where(system='http://hl7.org/fhir/sid/ndc').empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -517,7 +517,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
+    <t>A set of codes indicating the current status of an Immunization.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -548,6 +551,9 @@
     <t>example</t>
   </si>
   <si>
+    <t>The reason why a vaccine was not administered.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
@@ -560,20 +566,16 @@
     <t>Immunization.vaccineCode</t>
   </si>
   <si>
-    <t>Vaccine Product Type (bind to CVX)</t>
+    <t>Vaccine product administered</t>
   </si>
   <si>
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">us-core-5
-</t>
+    <t>The code for vaccine product administered.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/vaccine-code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -675,7 +677,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1878: source value from ADERS - 17_Vac1_TypeBrand (A-17.11)</t>
+    <t>1878: source value from ADERS - Vac1_TypeBrand (A-17.11)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -685,10 +687,6 @@
   </si>
   <si>
     <t>Immunization.patient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patient
-</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VAERSPatient)
@@ -701,7 +699,7 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
-    <t>1876: reference from ADERS - 0_Pt_ICN_Full (A-0)</t>
+    <t>1876: reference from ADERS - Pt_ICN_Full (A-0)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -933,6 +931,9 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -980,7 +981,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1883: source value from ADERS - 17_Vac1_Mfgr (A-17.13)</t>
+    <t>1883: source value from ADERS - Vac1_Mfgr (A-17.13)</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -992,7 +993,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1884: source value from ADERS - 17_Vac1_Lot (A-17.14)</t>
+    <t>1884: source value from ADERS - Vac1_Lot (A-17.14)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1038,7 +1039,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1885: source value from ADERS - 17_Vac1_Site (A-17.15)</t>
+    <t>1885: source value from ADERS - Vac1_Site (A-17.15)</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1086,7 +1087,7 @@
     <t>Immunization.route.text</t>
   </si>
   <si>
-    <t>1879: source value from ADERS - 17_Vac1_Route (A-17.12)</t>
+    <t>1879: source value from l (A-17.12)</t>
   </si>
   <si>
     <t>Immunization.doseQuantity</t>
@@ -1534,7 +1535,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1886: source value from ADERS - 17_Vac1_DoseInSeries (A-17.16)</t>
+    <t>1886: source value from ADERS - Vac1_DoseInSeries (A-17.16)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1888,7 +1889,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.8515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.24609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2074,9 +2075,7 @@
       <c r="M2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="N2" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>80</v>
@@ -3285,7 +3284,7 @@
         <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>92</v>
@@ -3331,9 +3330,11 @@
       <c r="X12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y12" s="2"/>
+      <c r="Y12" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="Z12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3372,16 +3373,16 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3389,10 +3390,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3406,7 +3407,7 @@
         <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>80</v>
@@ -3415,16 +3416,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3450,11 +3451,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3472,7 +3475,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3493,13 +3496,13 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3510,10 +3513,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3527,7 +3530,7 @@
         <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>80</v>
@@ -3536,13 +3539,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3569,11 +3572,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3591,7 +3596,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>91</v>
@@ -3600,7 +3605,7 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
@@ -3612,27 +3617,27 @@
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3655,13 +3660,13 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3712,7 +3717,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3739,7 +3744,7 @@
         <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>80</v>
@@ -3750,10 +3755,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3782,7 +3787,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3823,19 +3828,19 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3862,7 +3867,7 @@
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -3873,10 +3878,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3899,19 +3904,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3960,7 +3965,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3984,10 +3989,10 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -3998,10 +4003,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4024,19 +4029,19 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -4085,7 +4090,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4100,7 +4105,7 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>80</v>
@@ -4109,10 +4114,10 @@
         <v>80</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4123,14 +4128,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4206,7 +4211,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>91</v>
@@ -4382,7 +4387,7 @@
         <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
@@ -4445,7 +4450,7 @@
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>233</v>
@@ -4743,13 +4748,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -4881,7 +4886,7 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>262</v>
@@ -4916,7 +4921,7 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y25" t="s" s="2">
         <v>265</v>
@@ -5246,13 +5251,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5303,7 +5308,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5330,7 +5335,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5373,7 +5378,7 @@
         <v>138</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>140</v>
@@ -5414,19 +5419,19 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5453,7 +5458,7 @@
         <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>80</v>
@@ -5490,7 +5495,7 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>286</v>
@@ -5648,13 +5653,13 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>177</v>
+        <v>295</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5672,7 +5677,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5710,10 +5715,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5739,13 +5744,13 @@
         <v>149</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5795,7 +5800,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5822,7 +5827,7 @@
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5833,10 +5838,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5859,16 +5864,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5918,7 +5923,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5933,7 +5938,7 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5956,10 +5961,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5982,13 +5987,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6039,7 +6044,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6054,7 +6059,7 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>80</v>
@@ -6063,24 +6068,24 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6103,13 +6108,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6160,7 +6165,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6184,10 +6189,10 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6198,10 +6203,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6224,13 +6229,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6257,13 +6262,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -6281,7 +6286,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6296,7 +6301,7 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>80</v>
@@ -6305,24 +6310,24 @@
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6345,13 +6350,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6378,13 +6383,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6402,7 +6407,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6426,24 +6431,24 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6466,13 +6471,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6523,7 +6528,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6550,7 +6555,7 @@
         <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6561,10 +6566,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6593,7 +6598,7 @@
         <v>138</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>140</v>
@@ -6634,19 +6639,19 @@
         <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6673,7 +6678,7 @@
         <v>80</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6684,10 +6689,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6710,19 +6715,19 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6771,7 +6776,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6795,10 +6800,10 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -6809,10 +6814,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6835,19 +6840,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6896,7 +6901,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6911,7 +6916,7 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>80</v>
@@ -6920,10 +6925,10 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6934,10 +6939,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6960,13 +6965,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7017,7 +7022,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7041,10 +7046,10 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7055,10 +7060,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7081,13 +7086,13 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7138,7 +7143,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7159,13 +7164,13 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7176,10 +7181,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7202,13 +7207,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7259,7 +7264,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7286,7 +7291,7 @@
         <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7297,10 +7302,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7329,7 +7334,7 @@
         <v>138</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>140</v>
@@ -7382,7 +7387,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7409,7 +7414,7 @@
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7420,14 +7425,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7449,10 +7454,10 @@
         <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>140</v>
@@ -7507,7 +7512,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7545,10 +7550,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7571,13 +7576,13 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7604,13 +7609,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>177</v>
+        <v>295</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7628,7 +7633,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7649,13 +7654,13 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -7666,10 +7671,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7692,16 +7697,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7751,7 +7756,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -7772,16 +7777,16 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7789,10 +7794,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7815,13 +7820,13 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7872,7 +7877,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7893,13 +7898,13 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -7910,10 +7915,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7936,13 +7941,13 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7969,13 +7974,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -7993,7 +7998,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8014,13 +8019,13 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8031,10 +8036,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8057,13 +8062,13 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8114,7 +8119,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8135,7 +8140,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8152,10 +8157,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8181,20 +8186,20 @@
         <v>254</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="R52" t="s" s="2">
         <v>80</v>
@@ -8239,7 +8244,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8263,7 +8268,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>134</v>
@@ -8277,10 +8282,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8303,13 +8308,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8336,13 +8341,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8360,7 +8365,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8398,10 +8403,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8424,13 +8429,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8481,7 +8486,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8493,7 +8498,7 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8519,10 +8524,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8545,13 +8550,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8602,7 +8607,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8629,7 +8634,7 @@
         <v>80</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -8640,10 +8645,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8672,7 +8677,7 @@
         <v>138</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>140</v>
@@ -8725,7 +8730,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8752,7 +8757,7 @@
         <v>80</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -8763,14 +8768,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8792,10 +8797,10 @@
         <v>137</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>140</v>
@@ -8850,7 +8855,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8888,10 +8893,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8914,13 +8919,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8971,7 +8976,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8995,7 +9000,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>134</v>
@@ -9009,10 +9014,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9038,10 +9043,10 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9092,7 +9097,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9130,10 +9135,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9159,10 +9164,10 @@
         <v>246</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9213,7 +9218,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9237,7 +9242,7 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>134</v>
@@ -9251,10 +9256,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9280,10 +9285,10 @@
         <v>246</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9334,7 +9339,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9358,7 +9363,7 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>134</v>
@@ -9372,10 +9377,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9398,13 +9403,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9431,13 +9436,13 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9455,7 +9460,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9479,7 +9484,7 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>134</v>
@@ -9493,10 +9498,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9519,13 +9524,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9552,13 +9557,13 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -9576,7 +9581,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9614,10 +9619,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9640,16 +9645,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9699,7 +9704,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9723,10 +9728,10 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -9737,10 +9742,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9763,13 +9768,13 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9820,7 +9825,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9847,7 +9852,7 @@
         <v>80</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -9858,10 +9863,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9890,7 +9895,7 @@
         <v>138</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>140</v>
@@ -9943,7 +9948,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9970,7 +9975,7 @@
         <v>80</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -9981,14 +9986,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10010,10 +10015,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>140</v>
@@ -10068,7 +10073,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10106,10 +10111,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10135,10 +10140,10 @@
         <v>246</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10189,7 +10194,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10213,7 +10218,7 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>241</v>
@@ -10227,10 +10232,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10253,13 +10258,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10310,7 +10315,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10334,10 +10339,10 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>80</v>
@@ -10348,10 +10353,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10377,10 +10382,10 @@
         <v>254</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10431,7 +10436,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10455,10 +10460,10 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>80</v>
@@ -10469,10 +10474,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10495,13 +10500,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10552,7 +10557,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10590,10 +10595,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10616,13 +10621,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10673,7 +10678,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10700,7 +10705,7 @@
         <v>80</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>80</v>
@@ -10711,10 +10716,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10743,7 +10748,7 @@
         <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>140</v>
@@ -10796,7 +10801,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10823,7 +10828,7 @@
         <v>80</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>80</v>
@@ -10834,14 +10839,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10863,10 +10868,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -10921,7 +10926,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10959,10 +10964,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10985,13 +10990,13 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11042,7 +11047,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11080,10 +11085,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11109,10 +11114,10 @@
         <v>277</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11163,7 +11168,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11201,10 +11206,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11227,13 +11232,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11260,13 +11265,13 @@
         <v>80</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11284,7 +11289,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11322,10 +11327,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11348,16 +11353,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11402,10 +11407,10 @@
         <v>80</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>91</v>
@@ -11443,13 +11448,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>80</v>
@@ -11471,16 +11476,16 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11530,7 +11535,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>91</v>
@@ -11545,7 +11550,7 @@
         <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>80</v>
@@ -11568,10 +11573,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11594,16 +11599,16 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11653,7 +11658,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunization-vac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-vac1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="494">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to Immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Immunization</t>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-immunization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -274,11 +274,11 @@
     <t>Immunization event information</t>
   </si>
   <si>
-    <t>Describes the event of a patient being administered a vaccine or a record of an immunization as reported by a patient, a clinician or another party.</t>
+    <t>\-</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}us-core-5:SHOULD have a translation to the NDC value set {vaccineCode.coding.where(system='http://hl7.org/fhir/sid/ndc').empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -517,10 +517,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>A set of codes indicating the current status of an Immunization.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -551,9 +548,6 @@
     <t>example</t>
   </si>
   <si>
-    <t>The reason why a vaccine was not administered.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
@@ -566,16 +560,20 @@
     <t>Immunization.vaccineCode</t>
   </si>
   <si>
-    <t>Vaccine product administered</t>
+    <t>Vaccine Product Type (bind to CVX)</t>
   </si>
   <si>
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
-    <t>The code for vaccine product administered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/vaccine-code</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">us-core-5
+</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -677,7 +675,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1878: source value from ADERS - Vac1_TypeBrand (A-17.11)</t>
+    <t>1878: source value from ADERS - 17_Vac1_TypeBrand</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -687,6 +685,10 @@
   </si>
   <si>
     <t>Immunization.patient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient
+</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VAERSPatient)
@@ -699,7 +701,7 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
-    <t>1876: reference from ADERS - Pt_ICN_Full (A-0)</t>
+    <t>1876: reference from ADERS - 0_Pt_ICN_Full</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -784,7 +786,7 @@
 </t>
   </si>
   <si>
-    <t>1875: transform using concat(4_VacDate, 4_VacTime) on ADERS - (A-)</t>
+    <t>1875: transform using concat(4_VacDate, 4_VacTime)</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -931,9 +933,6 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -981,7 +980,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1883: source value from ADERS - Vac1_Mfgr (A-17.13)</t>
+    <t>1883: source value from ADERS - 17_Vac1_Mfgr</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -993,7 +992,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1884: source value from ADERS - Vac1_Lot (A-17.14)</t>
+    <t>1884: source value from ADERS - 17_Vac1_Lot</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1039,7 +1038,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1885: source value from ADERS - Vac1_Site (A-17.15)</t>
+    <t>1885: source value from ADERS - 17_Vac1_Site</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1087,7 +1086,7 @@
     <t>Immunization.route.text</t>
   </si>
   <si>
-    <t>1879: source value from l (A-17.12)</t>
+    <t>1879: source value from ADERS - 17_Vac1_Route</t>
   </si>
   <si>
     <t>Immunization.doseQuantity</t>
@@ -1535,7 +1534,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1886: source value from ADERS - Vac1_DoseInSeries (A-17.16)</t>
+    <t>1886: source value from ADERS - 17_Vac1_DoseInSeries</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1889,7 +1888,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.24609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.8515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2075,7 +2074,9 @@
       <c r="M2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="N2" s="2"/>
+      <c r="N2" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>80</v>
@@ -3284,7 +3285,7 @@
         <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>92</v>
@@ -3330,11 +3331,9 @@
       <c r="X12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Y12" s="2"/>
+      <c r="Z12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3373,16 +3372,16 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AN12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3390,10 +3389,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3407,7 +3406,7 @@
         <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>80</v>
@@ -3416,16 +3415,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3451,14 +3450,12 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y13" s="2"/>
+      <c r="Z13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
       </c>
@@ -3475,7 +3472,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3496,13 +3493,13 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3513,10 +3510,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3530,7 +3527,7 @@
         <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>80</v>
@@ -3539,13 +3536,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3572,13 +3569,11 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3596,7 +3591,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>91</v>
@@ -3605,7 +3600,7 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
@@ -3617,27 +3612,27 @@
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AP14" t="s" s="2">
+      <c r="AQ14" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>185</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3660,13 +3655,13 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3717,7 +3712,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3744,7 +3739,7 @@
         <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>80</v>
@@ -3755,10 +3750,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3787,7 +3782,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3828,19 +3823,19 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AC16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AD16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AD16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE16" t="s" s="2">
+      <c r="AF16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3867,7 +3862,7 @@
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -3878,10 +3873,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3904,19 +3899,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3965,7 +3960,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3989,10 +3984,10 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -4003,10 +3998,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4029,19 +4024,19 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -4090,7 +4085,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4105,19 +4100,19 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4128,14 +4123,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4211,7 +4206,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>91</v>
@@ -4387,7 +4382,7 @@
         <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
@@ -4450,7 +4445,7 @@
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>233</v>
@@ -4748,13 +4743,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -4886,7 +4881,7 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>262</v>
@@ -4921,7 +4916,7 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y25" t="s" s="2">
         <v>265</v>
@@ -5251,13 +5246,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5308,7 +5303,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5335,7 +5330,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5378,7 +5373,7 @@
         <v>138</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>140</v>
@@ -5419,19 +5414,19 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AC29" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC29" t="s" s="2">
+      <c r="AD29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE29" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AD29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE29" t="s" s="2">
+      <c r="AF29" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5458,7 +5453,7 @@
         <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>80</v>
@@ -5495,7 +5490,7 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>286</v>
@@ -5653,31 +5648,31 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y31" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="Y31" t="s" s="2">
+      <c r="Z31" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="Z31" t="s" s="2">
+      <c r="AA31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5715,10 +5710,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5744,13 +5739,13 @@
         <v>149</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5800,7 +5795,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5827,7 +5822,7 @@
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5838,10 +5833,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5864,16 +5859,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5923,7 +5918,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5938,7 +5933,7 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5961,10 +5956,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5987,13 +5982,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6044,7 +6039,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6059,33 +6054,33 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>317</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6108,13 +6103,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6165,7 +6160,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6189,10 +6184,10 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6203,10 +6198,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6229,13 +6224,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6262,14 +6257,14 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6286,7 +6281,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6301,33 +6296,33 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6350,13 +6345,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6383,14 +6378,14 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6407,7 +6402,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6431,24 +6426,24 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6471,13 +6466,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6528,7 +6523,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6555,7 +6550,7 @@
         <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6566,10 +6561,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6598,7 +6593,7 @@
         <v>138</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>140</v>
@@ -6639,19 +6634,19 @@
         <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AC39" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC39" t="s" s="2">
+      <c r="AD39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE39" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AD39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE39" t="s" s="2">
+      <c r="AF39" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6678,7 +6673,7 @@
         <v>80</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6689,10 +6684,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6715,19 +6710,19 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6776,7 +6771,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6800,10 +6795,10 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -6814,10 +6809,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6840,19 +6835,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6901,7 +6896,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6916,7 +6911,7 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>80</v>
@@ -6925,10 +6920,10 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6939,10 +6934,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6965,13 +6960,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7022,7 +7017,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7046,10 +7041,10 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7060,10 +7055,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7086,13 +7081,13 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7143,7 +7138,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7164,13 +7159,13 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7181,10 +7176,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7207,13 +7202,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7264,7 +7259,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7291,7 +7286,7 @@
         <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7302,10 +7297,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7334,7 +7329,7 @@
         <v>138</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>140</v>
@@ -7387,7 +7382,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7414,7 +7409,7 @@
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7425,14 +7420,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7454,10 +7449,10 @@
         <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>140</v>
@@ -7512,7 +7507,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7550,10 +7545,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7576,13 +7571,13 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7609,14 +7604,14 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>295</v>
+        <v>177</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7633,7 +7628,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7654,13 +7649,13 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -7671,10 +7666,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7697,16 +7692,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7756,7 +7751,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -7777,16 +7772,16 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AN48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7794,10 +7789,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7820,13 +7815,13 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7877,7 +7872,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7898,13 +7893,13 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -7915,10 +7910,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7941,13 +7936,13 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7974,14 +7969,14 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
       </c>
@@ -7998,7 +7993,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8019,13 +8014,13 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8036,10 +8031,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8062,13 +8057,13 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8119,7 +8114,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8140,7 +8135,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8157,10 +8152,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8186,20 +8181,20 @@
         <v>254</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="R52" t="s" s="2">
         <v>80</v>
@@ -8244,7 +8239,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8268,7 +8263,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>134</v>
@@ -8282,10 +8277,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8308,13 +8303,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8341,14 +8336,14 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>409</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8365,7 +8360,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8403,10 +8398,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8429,13 +8424,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8486,7 +8481,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8498,7 +8493,7 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8524,10 +8519,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8550,13 +8545,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8607,7 +8602,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8634,7 +8629,7 @@
         <v>80</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -8645,10 +8640,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8677,7 +8672,7 @@
         <v>138</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>140</v>
@@ -8730,7 +8725,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8757,7 +8752,7 @@
         <v>80</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -8768,14 +8763,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8797,10 +8792,10 @@
         <v>137</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>140</v>
@@ -8855,7 +8850,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8893,10 +8888,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8919,13 +8914,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8976,7 +8971,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9000,7 +8995,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>134</v>
@@ -9014,10 +9009,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9043,10 +9038,10 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9097,7 +9092,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9135,10 +9130,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9164,10 +9159,10 @@
         <v>246</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9218,7 +9213,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9242,7 +9237,7 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>134</v>
@@ -9256,10 +9251,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9285,10 +9280,10 @@
         <v>246</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9339,7 +9334,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9363,7 +9358,7 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>134</v>
@@ -9377,10 +9372,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9403,13 +9398,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9436,14 +9431,14 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>436</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
       </c>
@@ -9460,7 +9455,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9484,7 +9479,7 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>134</v>
@@ -9498,10 +9493,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9524,13 +9519,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9557,14 +9552,14 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>442</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
       </c>
@@ -9581,7 +9576,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9619,10 +9614,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9645,16 +9640,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9704,7 +9699,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9728,10 +9723,10 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -9742,10 +9737,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9768,13 +9763,13 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9825,7 +9820,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9852,7 +9847,7 @@
         <v>80</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -9863,10 +9858,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9895,7 +9890,7 @@
         <v>138</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>140</v>
@@ -9948,7 +9943,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9975,7 +9970,7 @@
         <v>80</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -9986,14 +9981,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10015,10 +10010,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>140</v>
@@ -10073,7 +10068,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10111,10 +10106,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10140,10 +10135,10 @@
         <v>246</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10194,7 +10189,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10218,7 +10213,7 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>241</v>
@@ -10232,10 +10227,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10258,13 +10253,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10315,7 +10310,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10339,10 +10334,10 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>80</v>
@@ -10353,10 +10348,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10382,10 +10377,10 @@
         <v>254</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10436,7 +10431,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10460,10 +10455,10 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>80</v>
@@ -10474,10 +10469,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10500,13 +10495,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10557,7 +10552,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10595,10 +10590,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10621,13 +10616,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10678,7 +10673,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10705,7 +10700,7 @@
         <v>80</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>80</v>
@@ -10716,10 +10711,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10748,7 +10743,7 @@
         <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>140</v>
@@ -10801,7 +10796,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10828,7 +10823,7 @@
         <v>80</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>80</v>
@@ -10839,14 +10834,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10868,10 +10863,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -10926,7 +10921,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10964,10 +10959,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10990,13 +10985,13 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11047,7 +11042,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11085,10 +11080,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11114,10 +11109,10 @@
         <v>277</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11168,7 +11163,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11206,10 +11201,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11232,13 +11227,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11265,14 +11260,14 @@
         <v>80</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>483</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
       </c>
@@ -11289,7 +11284,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11327,10 +11322,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11353,16 +11348,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11407,10 +11402,10 @@
         <v>80</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>91</v>
@@ -11448,13 +11443,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>80</v>
@@ -11476,16 +11471,16 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11535,7 +11530,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>91</v>
@@ -11550,7 +11545,7 @@
         <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>80</v>
@@ -11573,10 +11568,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11599,16 +11594,16 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M80" t="s" s="2">
-        <v>494</v>
-      </c>
       <c r="N80" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11658,7 +11653,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunization-vac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-vac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
